--- a/data/trans_orig/KIDMED_R3-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R3-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80325</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>71148</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89732</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>65887</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>55979</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>74315</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>55,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>85934</t>
+          <t>66868</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72586</t>
+          <t>58992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96767</t>
+          <t>74495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>151821</t>
+          <t>147193</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136183</t>
+          <t>134901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>166487</t>
+          <t>159375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>71,93%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31477</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50061</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>35822</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27394</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45730</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35,22%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49242</t>
+          <t>33481</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38409</t>
+          <t>25854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62590</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>85065</t>
+          <t>74365</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70399</t>
+          <t>62183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100703</t>
+          <t>86657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>48447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63728</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58988</t>
+          <t>58357</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>50548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66409</t>
+          <t>66929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>115447</t>
+          <t>115738</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102523</t>
+          <t>104150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126168</t>
+          <t>126535</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32499</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24928</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41433</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46,1%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>36933</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29664</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>44703</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>39,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>47,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>28481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43831</t>
+          <t>44862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>71654</t>
+          <t>69552</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60933</t>
+          <t>58755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84578</t>
+          <t>81140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39884</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33461</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44941</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>34535</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28746</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39782</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>68,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42459</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48916</t>
+          <t>41548</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>75977</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>67281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85005</t>
+          <t>83939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15960</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10903</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22383</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15554</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10307</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21343</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>31,05%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>35429</t>
+          <t>31877</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27417</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44864</t>
+          <t>40573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>126178</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>111666</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>139388</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>56,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>110399</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>74595</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>132143</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>51,22%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>61,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>134865</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119892</t>
+          <t>89884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148817</t>
+          <t>111886</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>245265</t>
+          <t>227838</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192805</t>
+          <t>209656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>271239</t>
+          <t>245049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71135</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>57925</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>85647</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>105138</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83394</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>140942</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>48,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>38,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>77793</t>
+          <t>74980</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63841</t>
+          <t>64754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92766</t>
+          <t>86756</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>182931</t>
+          <t>146115</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156957</t>
+          <t>128904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235391</t>
+          <t>164297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>86053</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>67077</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>98338</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>59,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>72398</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>61956</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>80976</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>62,68%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>93006</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70040</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106250</t>
+          <t>82798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>165404</t>
+          <t>161101</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>140394</t>
+          <t>142154</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182168</t>
+          <t>175924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>59533</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>47248</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>78509</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,93%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>43111</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>34533</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>53553</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>37,32%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66455</t>
+          <t>40418</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>32668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89421</t>
+          <t>49466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>109566</t>
+          <t>99951</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92802</t>
+          <t>85128</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134576</t>
+          <t>118898</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>42709</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>35383</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>49434</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>64,85%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>53,72%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>75,06%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>47884</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>41584</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>53830</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>69,5%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>60,36%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>78,13%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43938</t>
+          <t>49063</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>41500</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51009</t>
+          <t>54801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>91822</t>
+          <t>91773</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82104</t>
+          <t>81492</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101534</t>
+          <t>100748</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>23154</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16429</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>30480</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>46,28%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>21011</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15065</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>27311</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>30,5%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>39,64%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25093</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32885</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>46103</t>
+          <t>44447</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>35472</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55821</t>
+          <t>54728</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>432530</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>407333</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>456088</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>64,01%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>60,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>67,5%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>575</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>387562</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>329203</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>416766</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>60,07%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>51,03%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>64,6%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>459189</t>
+          <t>387090</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>428358</t>
+          <t>365390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>486251</t>
+          <t>405376</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>846751</t>
+          <t>819620</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>786273</t>
+          <t>785890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>884898</t>
+          <t>853967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>243165</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>219607</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>268362</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>35,99%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>32,5%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>39,72%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>327</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>257569</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>228365</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>315928</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>39,93%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35,4%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>48,97%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>273179</t>
+          <t>223142</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246117</t>
+          <t>204856</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>304010</t>
+          <t>244842</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>530748</t>
+          <t>466307</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>492601</t>
+          <t>431960</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>591226</t>
+          <t>500037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
